--- a/artfynd/A 16686-2026 artfynd.xlsx
+++ b/artfynd/A 16686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114588456</v>
+        <v>114588439</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Munga, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582588</v>
+        <v>582401</v>
       </c>
       <c r="R2" t="n">
-        <v>6622710</v>
+        <v>6622733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114588452</v>
+        <v>114588464</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Munga, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582450</v>
+        <v>582462</v>
       </c>
       <c r="R3" t="n">
-        <v>6622712</v>
+        <v>6622738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114588451</v>
+        <v>114588449</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +899,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582454</v>
+        <v>582550</v>
       </c>
       <c r="R4" t="n">
-        <v>6622694</v>
+        <v>6622722</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,12 +973,7 @@
         <v>114588450</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,15 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114588449</v>
+        <v>114588451</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,7 +1101,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582550</v>
+        <v>582454</v>
       </c>
       <c r="R6" t="n">
-        <v>6622722</v>
+        <v>6622694</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,12 +1140,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,50 +1172,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114588464</v>
+        <v>114588452</v>
       </c>
       <c r="B7" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Munga, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582462</v>
+        <v>582450</v>
       </c>
       <c r="R7" t="n">
-        <v>6622738</v>
+        <v>6622712</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,15 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114588454</v>
+        <v>114588453</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,7 +1303,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1351,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582583</v>
+        <v>582580</v>
       </c>
       <c r="R8" t="n">
-        <v>6622700</v>
+        <v>6622710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,50 +1374,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114588459</v>
+        <v>114588454</v>
       </c>
       <c r="B9" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Munga, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582539</v>
+        <v>582583</v>
       </c>
       <c r="R9" t="n">
-        <v>6622712</v>
+        <v>6622700</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,15 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114588453</v>
+        <v>114588456</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,7 +1505,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1559,7 +1514,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582580</v>
+        <v>582588</v>
       </c>
       <c r="R10" t="n">
         <v>6622710</v>
@@ -1624,12 +1579,7 @@
         <v>115031527</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,6 +1697,103 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114588459</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Munga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>582539</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6622712</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16686-2026 artfynd.xlsx
+++ b/artfynd/A 16686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588439</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588464</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588449</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588450</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588451</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588452</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588453</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588454</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588456</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115031527</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,8 +1849,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114588459</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>